--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,6 +1116,124 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129914632</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57749</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 56968, Mörghult, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>584506</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6401303</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spelade upp läte och fick omedelbart svar. Efter ngn minut kom både 1 hane o 1 hona och var väldigt irriterade! Optimal biotop för arten.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129907509</v>
       </c>
       <c r="B2" t="n">
-        <v>98822</v>
+        <v>98827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129907509</v>
       </c>
       <c r="B2" t="n">
-        <v>98827</v>
+        <v>98831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -792,7 +792,7 @@
         <v>129909609</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129909597</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129909677</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>129914632</v>
       </c>
       <c r="B6" t="n">
-        <v>57749</v>
+        <v>57750</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129907509</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129909609</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129909597</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129909677</v>
       </c>
       <c r="B5" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>129914632</v>
       </c>
       <c r="B6" t="n">
-        <v>57750</v>
+        <v>57753</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129907509</v>
       </c>
       <c r="B2" t="n">
-        <v>98834</v>
+        <v>98835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129907509</v>
       </c>
       <c r="B2" t="n">
-        <v>98835</v>
+        <v>98852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129909597</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129907509</v>
       </c>
       <c r="B2" t="n">
-        <v>98868</v>
+        <v>98870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129907509</v>
       </c>
       <c r="B2" t="n">
-        <v>98870</v>
+        <v>98957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129909609</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129909597</v>
       </c>
       <c r="B4" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129909677</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>129914632</v>
       </c>
       <c r="B6" t="n">
-        <v>57754</v>
+        <v>57839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129907509</v>
       </c>
       <c r="B2" t="n">
-        <v>98957</v>
+        <v>98870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129909609</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129909597</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>57900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129909677</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>129914632</v>
       </c>
       <c r="B6" t="n">
-        <v>57839</v>
+        <v>57754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1239,7 +1239,7 @@
         <v>131034108</v>
       </c>
       <c r="B7" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>131034178</v>
       </c>
       <c r="B8" t="n">
-        <v>91870</v>
+        <v>91871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>131034122</v>
       </c>
       <c r="B9" t="n">
-        <v>92413</v>
+        <v>92414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>129914632</v>
       </c>
       <c r="B6" t="n">
-        <v>57897</v>
+        <v>57839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1239,7 +1239,7 @@
         <v>131034108</v>
       </c>
       <c r="B7" t="n">
-        <v>91772</v>
+        <v>91774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>131034178</v>
       </c>
       <c r="B8" t="n">
-        <v>91871</v>
+        <v>91873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>131034122</v>
       </c>
       <c r="B9" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -1239,7 +1239,7 @@
         <v>131034108</v>
       </c>
       <c r="B7" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>131034178</v>
       </c>
       <c r="B8" t="n">
-        <v>91873</v>
+        <v>91874</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>131034122</v>
       </c>
       <c r="B9" t="n">
-        <v>92416</v>
+        <v>92417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56968-2025 artfynd.xlsx
+++ b/artfynd/A 56968-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129907509</v>
+        <v>131034122</v>
       </c>
       <c r="B2" t="n">
-        <v>98957</v>
+        <v>92510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>1143</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Blekticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Haploporus tuberculosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -710,29 +710,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ängnässjön, Sm</t>
+          <t>A 56968, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584488</v>
+        <v>584544</v>
       </c>
       <c r="R2" t="n">
-        <v>6401304</v>
+        <v>6401214</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,12 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På undersidan av grov gren på gammal ek. Högt upp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,54 +777,53 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129909609</v>
+        <v>131034178</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>91966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584485</v>
+        <v>584603</v>
       </c>
       <c r="R3" t="n">
-        <v>6401455</v>
+        <v>6401234</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,17 +861,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosök i låga</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +880,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129909597</v>
+        <v>131034108</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>91867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,35 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584537</v>
+        <v>584510</v>
       </c>
       <c r="R4" t="n">
-        <v>6401291</v>
+        <v>6401257</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,12 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,6 +989,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129909677</v>
+        <v>129914632</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1036,12 +1036,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1051,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584443</v>
+        <v>584506</v>
       </c>
       <c r="R5" t="n">
-        <v>6401398</v>
+        <v>6401303</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,17 +1089,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spår av födosök i barkborregran</t>
+          <t>Spelade upp läte och fick omedelbart svar. Efter ngn minut kom både 1 hane o 1 hona och var väldigt irriterade! Optimal biotop för arten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,34 +1119,34 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129914632</v>
+        <v>129909609</v>
       </c>
       <c r="B6" t="n">
-        <v>57839</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1146,20 +1154,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584506</v>
+        <v>584485</v>
       </c>
       <c r="R6" t="n">
-        <v>6401303</v>
+        <v>6401455</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spelade upp läte och fick omedelbart svar. Efter ngn minut kom både 1 hane o 1 hona och var väldigt irriterade! Optimal biotop för arten.</t>
+          <t>Födosök i låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,52 +1229,49 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131034108</v>
+        <v>129909677</v>
       </c>
       <c r="B7" t="n">
-        <v>91775</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5445</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584510</v>
+        <v>584443</v>
       </c>
       <c r="R7" t="n">
-        <v>6401257</v>
+        <v>6401398</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,12 +1309,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spår av födosök i barkborregran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,7 +1328,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1345,41 +1346,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131034178</v>
+        <v>129909597</v>
       </c>
       <c r="B8" t="n">
-        <v>91874</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5321</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1387,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584603</v>
+        <v>584537</v>
       </c>
       <c r="R8" t="n">
-        <v>6401234</v>
+        <v>6401291</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1417,17 +1423,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,7 +1437,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1455,32 +1455,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131034122</v>
+        <v>129907509</v>
       </c>
       <c r="B9" t="n">
-        <v>92417</v>
+        <v>99156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1143</v>
+        <v>219875</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blekticka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus tuberculosus</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1490,24 +1490,29 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 56968, Mörghult, Sm</t>
+          <t>Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584544</v>
+        <v>584488</v>
       </c>
       <c r="R9" t="n">
-        <v>6401214</v>
+        <v>6401304</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,17 +1536,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På undersidan av grov gren på gammal ek. Högt upp.</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,12 +1557,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
